--- a/EIT_2/MenschMaschinenSchnittstellen/NotenberechnungMicroquiz.xlsx
+++ b/EIT_2/MenschMaschinenSchnittstellen/NotenberechnungMicroquiz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mathias Lampert\Documents\Mathias Schule_Studium\FH\ELITE-Semester\EIT_2\MenschMaschinenSchnittstellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA4102E-77EA-4F30-9FDC-E5E0283475CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FCF28B-F2C6-4F08-8D77-F21B184022AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C39E4420-1B51-4646-B5DA-7C4527423F7C}"/>
   </bookViews>
@@ -129,16 +129,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -151,6 +158,933 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Prozentual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="accent1"/>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Tabelle1!$A$3:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Quiz 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Quiz 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Quiz 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Quiz 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Quiz 5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quiz 6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Quiz 7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Quiz 8</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$D$3:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>81.25</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>62.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-079A-4C71-B858-3B62C18D03D3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1"/>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="lt1">
+                      <a:alpha val="0"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:smooth val="0"/>
+        <c:axId val="1803563199"/>
+        <c:axId val="1803560319"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1803563199"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1803560319"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1803560319"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1803563199"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="229">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" spc="100" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>13139</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>6569</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagramm 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DC66C40-6DDC-4EA3-B21C-B9BC54BFF24A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C858FF68-3E66-4ABE-B399-E97E10EAAD15}" name="Tabelle1" displayName="Tabelle1" ref="A2:D11" totalsRowShown="0">
   <autoFilter ref="A2:D11" xr:uid="{C858FF68-3E66-4ABE-B399-E97E10EAAD15}"/>
@@ -158,7 +1092,7 @@
     <tableColumn id="1" xr3:uid="{11A90094-2E55-4987-A95F-D5B7E6F32AAA}" name="Spalte1"/>
     <tableColumn id="2" xr3:uid="{A78E1D48-E58E-4C98-935B-5D0BE2165961}" name="erreichte Punkte"/>
     <tableColumn id="3" xr3:uid="{7964B00E-2E1C-4A94-9259-8045415CF45C}" name="mögliche Punkte"/>
-    <tableColumn id="4" xr3:uid="{F41D67FF-20F2-4169-92EF-36038DC73A42}" name="Prozentual">
+    <tableColumn id="4" xr3:uid="{F41D67FF-20F2-4169-92EF-36038DC73A42}" name="Prozentual" dataDxfId="0">
       <calculatedColumnFormula>B3*100/C3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -483,7 +1417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971499B0-D794-46D7-8C6E-DB3D1BC7DE64}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -491,7 +1425,7 @@
     <col min="4" max="4" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -501,7 +1435,7 @@
       </c>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -514,8 +1448,14 @@
       <c r="D2" t="s">
         <v>12</v>
       </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -526,11 +1466,17 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <f>B3*100/C3</f>
+        <f t="shared" ref="D3:D11" si="0">B3*100/C3</f>
         <v>81.25</v>
       </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -541,11 +1487,17 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <f t="shared" ref="D4:D11" si="0">B4*100/C4</f>
+        <f t="shared" si="0"/>
         <v>31.25</v>
       </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -556,11 +1508,17 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <f>B5*100/C5</f>
+        <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -574,70 +1532,125 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="D7" t="e">
+      <c r="B7">
+        <v>2.5</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
+        <v>62.5</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="D8" t="e">
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" t="e">
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="D10" t="e">
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11">
         <f>SUM(B3:B10)</f>
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="C11">
-        <f>SUM(C3:C10)</f>
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
+        <v>42.1875</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F2:K11"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/EIT_2/MenschMaschinenSchnittstellen/NotenberechnungMicroquiz.xlsx
+++ b/EIT_2/MenschMaschinenSchnittstellen/NotenberechnungMicroquiz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mathias Lampert\Documents\Mathias Schule_Studium\FH\ELITE-Semester\EIT_2\MenschMaschinenSchnittstellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88FCF28B-F2C6-4F08-8D77-F21B184022AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36727EB9-7F1B-4495-BAAB-1BA45B874651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C39E4420-1B51-4646-B5DA-7C4527423F7C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t>Mikroquiz</t>
   </si>
@@ -141,7 +141,10 @@
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -292,10 +295,7 @@
                   <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>43.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -473,6 +473,271 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="34925" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+                <a:schemeClr val="accent1"/>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Tabelle1!$D$16:$D$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>56.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>43.75</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>75</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F380-4289-BC1E-753E60E9B575}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:dropLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="0">
+                    <a:schemeClr val="lt1"/>
+                  </a:gs>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="lt1">
+                      <a:alpha val="0"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:dropLines>
+        <c:smooth val="0"/>
+        <c:axId val="26884719"/>
+        <c:axId val="26886159"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="26884719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="26886159"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="26886159"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="26884719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -513,7 +778,576 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="229">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200" spc="100" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="ltUpDiag">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="lt1"/>
+        </a:bgClr>
+      </a:pattFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="lt1"/>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="lt1">
+                <a:alpha val="0"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="229">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -1082,6 +1916,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>11166</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>87366</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagramm 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A8F916F-9AA7-F8BF-D05A-36D55844A96A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1092,8 +1962,23 @@
     <tableColumn id="1" xr3:uid="{11A90094-2E55-4987-A95F-D5B7E6F32AAA}" name="Spalte1"/>
     <tableColumn id="2" xr3:uid="{A78E1D48-E58E-4C98-935B-5D0BE2165961}" name="erreichte Punkte"/>
     <tableColumn id="3" xr3:uid="{7964B00E-2E1C-4A94-9259-8045415CF45C}" name="mögliche Punkte"/>
-    <tableColumn id="4" xr3:uid="{F41D67FF-20F2-4169-92EF-36038DC73A42}" name="Prozentual" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{F41D67FF-20F2-4169-92EF-36038DC73A42}" name="Prozentual" dataDxfId="1">
       <calculatedColumnFormula>B3*100/C3</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DEC0852F-A523-47B4-98B0-4D06EEF5E7F2}" name="Tabelle13" displayName="Tabelle13" ref="A15:D24" totalsRowShown="0">
+  <autoFilter ref="A15:D24" xr:uid="{DEC0852F-A523-47B4-98B0-4D06EEF5E7F2}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{C11FE0B2-8960-4983-B027-3B001B7DD14A}" name="Spalte1"/>
+    <tableColumn id="2" xr3:uid="{24A9E73B-021E-46CD-82A1-3C9C07E02B06}" name="erreichte Punkte"/>
+    <tableColumn id="3" xr3:uid="{8FA8211F-6D93-489E-BAB3-8D820F68ACDC}" name="mögliche Punkte"/>
+    <tableColumn id="4" xr3:uid="{7F3214E1-9BF7-4975-8304-D263DCA85660}" name="Prozentual" dataDxfId="0">
+      <calculatedColumnFormula>B16*100/C16</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1417,15 +2302,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{971499B0-D794-46D7-8C6E-DB3D1BC7DE64}">
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" customWidth="1"/>
+    <col min="3" max="3" width="16.81640625" customWidth="1"/>
+    <col min="4" max="4" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" ht="23.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1435,7 +2320,7 @@
       </c>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1455,7 +2340,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -1476,7 +2361,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1497,7 +2382,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -1518,7 +2403,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -1539,7 +2424,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -1560,7 +2445,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1581,16 +2466,19 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>8</v>
       </c>
+      <c r="B9">
+        <v>1.75</v>
+      </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>43.75</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -1599,16 +2487,9 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>9</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>0</v>
       </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -1617,20 +2498,20 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11">
         <f>SUM(B3:B10)</f>
-        <v>13.5</v>
+        <v>15.25</v>
       </c>
       <c r="C11">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>42.1875</v>
+        <v>54.464285714285715</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
@@ -1639,18 +2520,175 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
+    <row r="14" spans="1:11" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" t="e">
+        <f t="shared" ref="D16:D24" si="1">B16*100/C16</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17">
+        <v>1.75</v>
+      </c>
+      <c r="C17">
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="1"/>
+        <v>43.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
+      </c>
+      <c r="C18">
+        <v>4</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>2.25</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="1"/>
+        <v>56.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22">
+        <v>1.75</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>43.75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+      <c r="C23">
+        <v>4</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24">
+        <f>SUM(B16:B23)</f>
+        <v>18.75</v>
+      </c>
+      <c r="C24">
+        <v>28</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>66.964285714285708</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="F2:K11"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C14:D14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>